--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_5d/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_5d/close/close_backtest_metrics.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parameters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'performance'!$A$1:$C$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'parameters'!$A$1:$C$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'performance'!$A$1:$C$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'parameters'!$A$1:$C$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2021-02-01至2026-07-31</t>
+          <t>2021-02-01至2026-07-30</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="4">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.010125181193571</v>
+        <v>1.014116230297413</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.01012518119357741</v>
+        <v>0.0141162302974196</v>
       </c>
     </row>
     <row r="7">
@@ -593,37 +593,37 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.001909194174624984</v>
+        <v>0.002659482107271183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>绝对风险收益</t>
+          <t>收益表现</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>策略年化波动率</t>
+          <t>中证A500年化收益率</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.2485023598116495</v>
+        <v>-0.01683193623386603</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>绝对风险收益</t>
+          <t>收益表现</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sharpe</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0.07179624369664606</v>
+          <t>年化超额收益</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.01982511338546988</v>
       </c>
     </row>
     <row r="10">
@@ -634,11 +634,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sortino</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0.1032350133898298</v>
+          <t>策略年化波动率</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2485895265556103</v>
       </c>
     </row>
     <row r="11">
@@ -649,11 +649,11 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>策略最大回撤</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.5647149552321514</v>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.07486967933505913</v>
       </c>
     </row>
     <row r="12">
@@ -664,13 +664,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>策略最大回撤区间</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2021年09月-2024年09月</t>
-        </is>
+          <t>Sortino</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.1076570155494794</v>
       </c>
     </row>
     <row r="13">
@@ -681,105 +679,199 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Calmar</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0.003380810366249507</v>
+          <t>策略最大回撤</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5647149552321514</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>交易与组合</t>
+          <t>绝对风险收益</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>年化换手率（单边）</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>26.1430788016743</v>
+          <t>策略最大回撤区间</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2021年09月-2024年09月</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>交易与组合</t>
+          <t>绝对风险收益</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>平均单次换仓比率（单边）</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0.1041335616277277</v>
+          <t>Calmar</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.004709423900732155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>交易与组合</t>
+          <t>相对基准表现</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>累计交易成本率</t>
+          <t>年化跟踪误差</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2420951032815151</v>
+        <v>0.1704226231181568</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>交易与组合</t>
+          <t>相对基准表现</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>平均持仓ETF数量</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>8.309541697971451</v>
+          <t>IR</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0.1887292898828717</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>交易与组合</t>
+          <t>相对基准表现</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>调仓次数</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>1331</v>
+          <t>超额最大回撤</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3152197235957077</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>相对基准表现</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>超额最大回撤区间</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2021年09月-2025年08月</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>交易与组合</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>年化换手率（单边）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>26.15214065362547</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>交易与组合</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>平均单次换仓比率（单边）</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.1041699522890742</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>交易与组合</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>累计交易成本率</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.2420103358794148</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>交易与组合</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>平均持仓ETF数量</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>8.306766917293233</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>交易与组合</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>调仓次数</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>交易与组合</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>调仓成功率</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C19"/>
+  <autoFilter ref="A1:C25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -790,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -835,47 +927,51 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>趋势策略</t>
+          <t>基准设置</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>聚类相关性阈值</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>0.9</v>
+          <t>基准名称</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>中证A500</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>趋势策略</t>
+          <t>基准设置</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>趋势因子窗口</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>20</v>
+          <t>基准代码</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>000510.CSI</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>趋势策略</t>
+          <t>基准设置</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>排名得分公式</t>
+          <t>超额净值</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>收益率÷波动率</t>
+          <t>策略累计净值÷基准累计净值；共同起点为1</t>
         </is>
       </c>
     </row>
@@ -887,128 +983,126 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>调仓日入选比例</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0.1</v>
+          <t>聚类相关性阈值</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>趋势过滤</t>
+          <t>趋势策略</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>过滤位置</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>排名后</t>
-        </is>
+          <t>趋势因子窗口</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>趋势过滤</t>
+          <t>趋势策略</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>过滤条件</t>
+          <t>排名得分公式</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>当前趋势窗口收益率&gt;0</t>
+          <t>收益率÷波动率</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>趋势过滤</t>
+          <t>趋势策略</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>未通过处理</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>不向后补选，空缺权重留现金</t>
-        </is>
+          <t>调仓日入选比例</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ETF选择</t>
+          <t>趋势过滤</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>代表ETF选择</t>
+          <t>过滤位置</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>跟踪同一指数中当日成交量最大</t>
+          <t>排名后</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>账户结构</t>
+          <t>趋势过滤</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>调仓模式</t>
+          <t>过滤条件</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>staggered</t>
+          <t>当前趋势窗口收益率&gt;0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>账户结构</t>
+          <t>趋势过滤</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>组合结构</t>
+          <t>未通过处理</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5个独立账户逐日错峰持有5个交易日</t>
+          <t>不向后补选，空缺权重留现金</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>账户结构</t>
+          <t>ETF选择</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>账户数量</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>5</v>
+          <t>代表ETF选择</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>跟踪同一指数中当日成交量最大</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1019,11 +1113,13 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>每账户初始资金比例</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.2</v>
+          <t>调仓模式</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>staggered</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1034,12 +1130,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>计划调仓账户数</t>
+          <t>组合结构</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>每个交易日1个</t>
+          <t>5个独立账户逐日错峰持有5个交易日</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1147,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>单账户调仓间隔（交易日）</t>
+          <t>账户数量</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -1066,188 +1162,235 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>账户之间资金转移</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>无；各账户独立复利并保留自己的现金</t>
-        </is>
+          <t>每账户初始资金比例</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>交易设置</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>初始净值 NAV₀</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>1</v>
+          <t>计划调仓账户数</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>每个交易日1个</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>收益参数</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>年化无风险利率 r_f</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>0.015</v>
+          <t>单账户调仓间隔（交易日）</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>交易成本</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>买入成本 c_buy</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>0.001</v>
+          <t>账户之间资金转移</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>无；各账户独立复利并保留自己的现金</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>交易成本</t>
+          <t>交易设置</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>卖出成本 c_sell</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0.001</v>
+          <t>初始净值 NAV₀</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>交易成本</t>
+          <t>收益参数</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>完整换仓成本 T_c</t>
+          <t>年化无风险利率 r_f</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>容量参数</t>
+          <t>交易成本</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>当日成交额使用比例 ρ_amt</t>
+          <t>买入成本 c_buy</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.1</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>容量参数</t>
+          <t>交易成本</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>倒序分位 q_desc</t>
+          <t>卖出成本 c_sell</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.95</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>容量参数</t>
+          <t>交易成本</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>等价升序分位 q_asc</t>
+          <t>完整换仓成本 T_c</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>组合约束</t>
+          <t>容量参数</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>指数权重</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>按过滤前计划入选数量等权</t>
-        </is>
+          <t>当日成交额使用比例 ρ_amt</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>收益口径</t>
+          <t>容量参数</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>扣费后收益</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>买入和卖出均扣除交易成本</t>
-        </is>
+          <t>倒序分位 q_desc</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>容量参数</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>等价升序分位 q_asc</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>组合约束</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>指数权重</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>按过滤前计划入选数量等权</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>收益口径</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>扣费后收益</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>买入和卖出均扣除交易成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>容量口径</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>组合容量</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>各持仓ETF容量的5%分位</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C28"/>
+  <autoFilter ref="A1:C31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>